--- a/Excel/Enterprises/Enterprise_Feedlot_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Feedlot_Template_WIP_v01.xlsx
@@ -603,9 +603,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -613,9 +613,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -624,9 +624,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -634,9 +634,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -660,9 +660,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -670,9 +670,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -1254,108 +1254,106 @@
   </numFmts>
   <fonts count="55" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1366,219 +1364,217 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -1586,34 +1582,34 @@
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF0C769E"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2463,11 +2459,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2487,11 +2482,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2511,11 +2505,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2535,11 +2528,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2559,11 +2551,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2583,11 +2574,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2607,11 +2597,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2631,11 +2620,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2655,11 +2643,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2679,11 +2666,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2703,11 +2689,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2727,11 +2712,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2751,11 +2735,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2775,11 +2758,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2799,11 +2781,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2823,11 +2804,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2847,11 +2827,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2871,11 +2850,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2895,11 +2873,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2919,11 +2896,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2943,11 +2919,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2967,11 +2942,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2991,11 +2965,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3015,11 +2988,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3039,11 +3011,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3063,11 +3034,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3087,11 +3057,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3111,11 +3080,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3135,11 +3103,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3159,11 +3126,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3183,11 +3149,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3207,11 +3172,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3231,11 +3195,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3255,11 +3218,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3279,11 +3241,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3303,11 +3264,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3327,11 +3287,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3351,11 +3310,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3375,11 +3333,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3399,11 +3356,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3423,11 +3379,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3734,7 +3689,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4199,7 +4154,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4436,7 +4391,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4573,7 +4528,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -5978,24 +5933,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{6496CA75-FED4-4E21-A81D-BDC20736B7B5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6059,24 +6014,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{1A778010-8EF6-4986-9F7A-ED1F5F66D6A5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6140,24 +6095,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{7DC837A9-60D0-4FEE-9D60-F5F33C8747DB}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6221,24 +6176,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A1C4261C-1106-48B4-9C10-E82D60412011}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6302,24 +6257,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{AE965B10-5BD0-44CC-8118-41596A6F15E2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6383,24 +6338,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{304D704D-8D75-4B25-B661-1CD4BF80A14D}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6463,16 +6418,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6538,36 +6493,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6633,18 +6588,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6712,7 +6667,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -6830,16 +6785,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6905,36 +6860,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7000,18 +6955,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7179,16 +7134,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7254,36 +7209,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7349,18 +7304,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7422,7 +7377,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7446,7 +7401,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7514,7 +7469,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -7637,16 +7592,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7712,36 +7667,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7807,18 +7762,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7990,7 +7945,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8014,7 +7969,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8076,7 +8031,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8100,7 +8055,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8162,7 +8117,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8186,7 +8141,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8248,7 +8203,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8272,7 +8227,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8334,7 +8289,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8358,7 +8313,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8420,7 +8375,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8444,7 +8399,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8506,7 +8461,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8530,7 +8485,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8599,24 +8554,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{325659CC-BF18-4027-9C39-6B59F0E2F578}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8680,24 +8635,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A9E71E38-28CF-40B4-A787-CD2A933BF092}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8761,24 +8716,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{FBAAA7CE-3F73-42A7-B887-E644937F7159}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8842,24 +8797,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{E266E2BA-6A96-4903-9E52-5C6BCFEF9FF1}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8923,24 +8878,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{F8F36783-2D83-448C-9BE3-D1653ADA37CE}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9004,24 +8959,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9792A2EE-0599-40C6-BEC6-FB928C51F2CA}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9085,24 +9040,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9FBD39D1-A40C-4D41-815F-1614BABEEB25}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9166,24 +9121,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{48E1D669-5050-474F-B029-B219812AC417}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9246,16 +9201,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9321,36 +9276,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9416,18 +9371,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9495,7 +9450,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -9613,16 +9568,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9688,36 +9643,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9783,18 +9738,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9962,16 +9917,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10037,36 +9992,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10132,18 +10087,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10205,7 +10160,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10229,7 +10184,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10297,7 +10252,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -10420,16 +10375,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10495,18 +10450,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10678,7 +10633,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10747,7 +10702,7 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10815,7 +10770,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10839,7 +10794,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10902,7 +10857,7 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10971,7 +10926,7 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11039,7 +10994,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11053,7 +11008,7 @@
             <a:t>t CO2-e / tonne manure</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11067,7 +11022,7 @@
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11091,7 +11046,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11153,7 +11108,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11177,7 +11132,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11246,24 +11201,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{B945A79A-D657-45FF-8794-B3F7FE79A7B2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11327,24 +11282,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A0887E06-5564-4610-905A-7D5E4A0E50F4}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11407,7 +11362,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Liveweight sold</a:t>
           </a:r>
         </a:p>
@@ -11544,7 +11499,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Manure sold</a:t>
           </a:r>
         </a:p>
@@ -12425,12 +12380,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -12641,31 +12596,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="80" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="81" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12683,7 +12638,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -12711,7 +12666,7 @@
       <c r="J1" s="91"/>
       <c r="K1" s="91"/>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -12723,7 +12678,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -12738,7 +12693,7 @@
       <c r="J3" s="92"/>
       <c r="K3" s="92"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -12748,10 +12703,10 @@
         <v>Emissions breakdown for activities running between 01 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -12759,13 +12714,13 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -12790,7 +12745,7 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>284</v>
@@ -12818,7 +12773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -12848,7 +12803,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -12879,7 +12834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -12910,7 +12865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -12941,7 +12896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -12972,7 +12927,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>135</v>
@@ -13000,7 +12955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -13030,7 +12985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -13061,7 +13016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -13092,7 +13047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13123,7 +13078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13146,20 +13101,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="D23" s="78" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="12" t="s">
         <v>238</v>
       </c>
@@ -13180,7 +13135,7 @@
       </c>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="e" cm="1">
         <f t="array" ref="D26">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13208,7 +13163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="86" t="s">
         <v>239</v>
       </c>
@@ -13227,15 +13182,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="78" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
         <v>241</v>
       </c>
@@ -13256,7 +13211,7 @@
       </c>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="s">
         <v>287</v>
       </c>
@@ -13283,7 +13238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
         <v>269</v>
       </c>
@@ -13310,7 +13265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
         <v>242</v>
       </c>
@@ -13337,7 +13292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="s">
         <v>243</v>
       </c>
@@ -13364,7 +13319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="s">
         <v>270</v>
       </c>
@@ -13391,7 +13346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="1" t="s">
         <v>244</v>
       </c>
@@ -13418,7 +13373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="1" t="s">
         <v>245</v>
       </c>
@@ -13445,7 +13400,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="e" cm="1">
         <f t="array" ref="D40">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13473,7 +13428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
         <v>247</v>
       </c>
@@ -13500,7 +13455,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
         <v>246</v>
       </c>
@@ -13527,7 +13482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
         <v>248</v>
       </c>
@@ -13554,7 +13509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="86" t="s">
         <v>249</v>
       </c>
@@ -13573,16 +13528,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="78" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="86" t="s">
         <v>250</v>
       </c>
@@ -13594,16 +13549,16 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="78" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="53" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="12"/>
       <c r="E54" s="12" t="s">
         <v>131</v>
@@ -13613,7 +13568,7 @@
       </c>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="95" t="s">
         <v>251</v>
       </c>
@@ -13629,7 +13584,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="95" t="s">
         <v>253</v>
       </c>
@@ -13645,37 +13600,37 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13689,7 +13644,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:P56"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -13699,7 +13654,7 @@
     <col min="14" max="16" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="91" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="91" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -13707,8 +13662,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C3" s="92"/>
       <c r="D3" s="92"/>
       <c r="E3" s="92"/>
@@ -13724,13 +13679,13 @@
       <c r="O3" s="92"/>
       <c r="P3" s="92"/>
     </row>
-    <row r="32" spans="4:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
         <v>131</v>
@@ -13740,7 +13695,7 @@
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="76" t="s">
         <v>254</v>
       </c>
@@ -13756,7 +13711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="76" t="s">
         <v>255</v>
       </c>
@@ -13772,18 +13727,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D42" s="78" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="12" t="s">
         <v>133</v>
       </c>
@@ -13806,7 +13761,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="s">
         <v>275</v>
       </c>
@@ -13833,7 +13788,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="s">
         <v>276</v>
       </c>
@@ -13860,7 +13815,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>277</v>
       </c>
@@ -13887,7 +13842,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="s">
         <v>278</v>
       </c>
@@ -13914,7 +13869,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="s">
         <v>279</v>
       </c>
@@ -13936,12 +13891,12 @@
       </c>
       <c r="J48" s="10"/>
     </row>
-    <row r="50" spans="4:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D50" s="78" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="12" t="s">
         <v>133</v>
       </c>
@@ -13964,7 +13919,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="1" t="s">
         <v>275</v>
       </c>
@@ -13991,7 +13946,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="s">
         <v>276</v>
       </c>
@@ -14018,7 +13973,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="s">
         <v>277</v>
       </c>
@@ -14045,7 +14000,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="s">
         <v>278</v>
       </c>
@@ -14072,7 +14027,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="s">
         <v>279</v>
       </c>
@@ -14107,7 +14062,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="22" customWidth="1"/>
@@ -14128,7 +14083,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="22" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -14139,7 +14094,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14166,7 +14121,7 @@
       <c r="W3" s="24"/>
       <c r="X3" s="24"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14181,19 +14136,19 @@
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="N5" s="31"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="33"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14205,7 +14160,7 @@
       <c r="F7" s="44"/>
       <c r="G7" s="45"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -14217,14 +14172,14 @@
       <c r="F8" s="47"/>
       <c r="G8" s="48"/>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="49"/>
       <c r="F9" s="17"/>
       <c r="N9" s="35"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -14239,7 +14194,7 @@
       </c>
       <c r="N10" s="35"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -14256,7 +14211,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="40"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -14271,7 +14226,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -14288,7 +14243,7 @@
       <c r="N13" s="42"/>
       <c r="O13" s="42"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -14305,7 +14260,7 @@
       <c r="N14" s="42"/>
       <c r="O14" s="42"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>109</v>
@@ -14319,7 +14274,7 @@
       <c r="N15" s="42"/>
       <c r="O15" s="42"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -14335,7 +14290,7 @@
       <c r="N16" s="42"/>
       <c r="O16" s="42"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -14350,7 +14305,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -14364,7 +14319,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14379,7 +14334,7 @@
       <c r="G19" s="50"/>
       <c r="N19" s="31"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14395,7 +14350,7 @@
       <c r="G20" s="49"/>
       <c r="N20" s="33"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>115</v>
@@ -14407,7 +14362,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="49"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -14418,29 +14373,29 @@
       </c>
       <c r="G22" s="53"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="33"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="L30" s="51"/>
       <c r="M30" s="51"/>
@@ -14457,7 +14412,7 @@
       <c r="X30" s="51"/>
       <c r="Y30" s="51"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="L31" s="52"/>
       <c r="M31" s="52"/>
@@ -14474,7 +14429,7 @@
       <c r="X31" s="52"/>
       <c r="Y31" s="52"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="L32" s="52"/>
       <c r="M32" s="52"/>
@@ -14491,7 +14446,7 @@
       <c r="X32" s="52"/>
       <c r="Y32" s="52"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="L33" s="52"/>
       <c r="M33" s="52"/>
@@ -14508,7 +14463,7 @@
       <c r="X33" s="52"/>
       <c r="Y33" s="52"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="54"/>
       <c r="K34" s="55"/>
@@ -14527,7 +14482,7 @@
       <c r="X34" s="52"/>
       <c r="Y34" s="52"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="54"/>
       <c r="K35" s="55"/>
@@ -14546,7 +14501,7 @@
       <c r="X35" s="52"/>
       <c r="Y35" s="52"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="56"/>
       <c r="E36" s="56"/>
@@ -14571,7 +14526,7 @@
       <c r="X36" s="52"/>
       <c r="Y36" s="52"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="56"/>
       <c r="E37" s="56"/>
@@ -14596,7 +14551,7 @@
       <c r="X37" s="52"/>
       <c r="Y37" s="52"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="56"/>
       <c r="E38" s="56"/>
@@ -14621,7 +14576,7 @@
       <c r="X38" s="52"/>
       <c r="Y38" s="52"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="56"/>
       <c r="E39" s="56"/>
@@ -14646,7 +14601,7 @@
       <c r="X39" s="52"/>
       <c r="Y39" s="52"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
@@ -14671,96 +14626,96 @@
       <c r="X40" s="62"/>
       <c r="Y40" s="62"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="63"/>
       <c r="E47" s="63"/>
       <c r="F47" s="63"/>
       <c r="G47" s="63"/>
       <c r="H47" s="63"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="64"/>
       <c r="E48" s="64"/>
       <c r="F48" s="65"/>
       <c r="G48" s="65"/>
       <c r="H48" s="64"/>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="64"/>
       <c r="E49" s="64"/>
       <c r="F49" s="65"/>
       <c r="G49" s="65"/>
       <c r="H49" s="64"/>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="64"/>
       <c r="E50" s="64"/>
       <c r="F50" s="65"/>
       <c r="G50" s="65"/>
       <c r="H50" s="64"/>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="66"/>
       <c r="E51" s="67"/>
       <c r="F51" s="67"/>
       <c r="G51" s="67"/>
       <c r="H51" s="68"/>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="69"/>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F57" s="70"/>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E58" s="71"/>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E59" s="71"/>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E60" s="72"/>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="71"/>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="71"/>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="72"/>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="73"/>
       <c r="E69" s="73"/>
       <c r="F69" s="73"/>
@@ -14768,7 +14723,7 @@
       <c r="H69" s="73"/>
       <c r="I69" s="73"/>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="73"/>
       <c r="E70" s="73"/>
       <c r="F70" s="73"/>
@@ -14776,7 +14731,7 @@
       <c r="H70" s="73"/>
       <c r="I70" s="73"/>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="73"/>
       <c r="E71" s="73"/>
       <c r="F71" s="73"/>
@@ -14784,7 +14739,7 @@
       <c r="H71" s="73"/>
       <c r="I71" s="73"/>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="73"/>
       <c r="E72" s="73"/>
       <c r="F72" s="73"/>
@@ -14792,59 +14747,59 @@
       <c r="H72" s="73"/>
       <c r="I72" s="73"/>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="74"/>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="74"/>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="74"/>
     </row>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="74"/>
     </row>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="74"/>
     </row>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -14870,7 +14825,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J78"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14881,7 +14836,7 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="28" t="s">
         <v>140</v>
       </c>
@@ -14893,7 +14848,7 @@
       <c r="I1" s="22"/>
       <c r="J1" s="22"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -14903,7 +14858,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
@@ -14913,7 +14868,7 @@
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
     </row>
-    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>88</v>
       </c>
@@ -14921,13 +14876,13 @@
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="32"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>89</v>
       </c>
@@ -14937,7 +14892,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="25"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="13" t="s">
         <v>91</v>
       </c>
@@ -14947,13 +14902,13 @@
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="36" t="s">
         <v>93</v>
       </c>
@@ -14961,13 +14916,13 @@
       <c r="F10" s="38"/>
       <c r="G10" s="39"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
@@ -14979,7 +14934,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
@@ -14992,16 +14947,16 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
     </row>
-    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
@@ -15012,7 +14967,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
@@ -15023,7 +14978,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
@@ -15035,7 +14990,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="s">
         <v>266</v>
       </c>
@@ -15047,7 +15002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="s">
         <v>267</v>
       </c>
@@ -15058,7 +15013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="s">
         <v>273</v>
       </c>
@@ -15069,7 +15024,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="s">
         <v>274</v>
       </c>
@@ -15080,7 +15035,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D27" s="1" t="s">
         <v>271</v>
       </c>
@@ -15091,7 +15046,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="1" t="s">
         <v>272</v>
       </c>
@@ -15102,18 +15057,18 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D31" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D34" s="78" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2025 to 31, December, 2025 from environmental plantings</v>
       </c>
     </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="20" t="s">
         <v>230</v>
       </c>
@@ -15127,7 +15082,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="34"/>
       <c r="E37" s="75"/>
       <c r="F37" s="19"/>
@@ -15136,29 +15091,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D41" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="43" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D43" s="78" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="45" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="88" t="str" cm="1">
         <f t="array" ref="D45">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 2 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="79" t="s">
         <v>116</v>
       </c>
@@ -15169,7 +15124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="str" cm="1">
         <f t="array" ref="D49:D50">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15186,7 +15141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15202,7 +15157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E51" s="75">
         <f>IF(ISBLANK($D51), 0, IF(ISNUMBER(SEARCH("reporting", $D51)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15215,7 +15170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E52" s="75">
         <f>IF(ISBLANK($D52), 0, IF(ISNUMBER(SEARCH("reporting", $D52)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15228,7 +15183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E53" s="75">
         <f>IF(ISBLANK($D53), 0, IF(ISNUMBER(SEARCH("reporting", $D53)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15241,7 +15196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="89" t="s">
         <v>129</v>
       </c>
@@ -15257,13 +15212,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D59" s="78" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="61" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D61" s="79" t="s">
         <v>116</v>
       </c>
@@ -15272,7 +15227,7 @@
       </c>
       <c r="F61" s="79"/>
     </row>
-    <row r="62" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D62" s="1" t="str" cm="1">
         <f t="array" ref="D62:D63">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15285,7 +15240,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D63" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15297,7 +15252,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E64" s="75">
         <f>IF(ISBLANK($D64), 0, IF(ISNUMBER(SEARCH("reporting", $D64)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15306,7 +15261,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E65" s="75">
         <f>IF(ISBLANK($D65), 0, IF(ISNUMBER(SEARCH("reporting", $D65)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15315,7 +15270,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E66" s="75">
         <f>IF(ISBLANK($D66), 0, IF(ISNUMBER(SEARCH("reporting", $D66)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15324,7 +15279,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="89" t="s">
         <v>130</v>
       </c>
@@ -15336,13 +15291,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D70" s="78" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D72" s="79" t="s">
         <v>116</v>
       </c>
@@ -15353,7 +15308,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D73" s="1" t="str" cm="1">
         <f t="array" ref="D73:D74">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15370,7 +15325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D74" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15386,7 +15341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E75" s="75">
         <f>IF(ISBLANK($D75), 0, IF(ISNUMBER(SEARCH("reporting", $D75)), E51-$E$64, "Enter value"))</f>
         <v>0</v>
@@ -15399,7 +15354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E76" s="75">
         <f>IF(ISBLANK($D76), 0, IF(ISNUMBER(SEARCH("reporting", $D76)), E52-$E$65, "Enter value"))</f>
         <v>0</v>
@@ -15412,7 +15367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E77" s="75">
         <f>IF(ISBLANK($D77), 0, IF(ISNUMBER(SEARCH("reporting", $D77)), E53-$E$66, "Enter value"))</f>
         <v>0</v>
@@ -15425,7 +15380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="89" t="s">
         <v>129</v>
       </c>
@@ -15455,7 +15410,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15469,8 +15424,8 @@
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
@@ -15483,13 +15438,13 @@
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
     </row>
-    <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="88" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="20" t="s">
         <v>260</v>
       </c>
@@ -15509,7 +15464,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="34"/>
       <c r="E7" s="14"/>
       <c r="F7" s="98">
@@ -15526,7 +15481,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="34"/>
       <c r="E8" s="14"/>
       <c r="F8" s="98"/>
@@ -15537,7 +15492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="34"/>
       <c r="E9" s="14"/>
       <c r="F9" s="98"/>
@@ -15548,7 +15503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="34"/>
       <c r="E10" s="14"/>
       <c r="F10" s="98"/>
@@ -15559,7 +15514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="34"/>
       <c r="E11" s="14"/>
       <c r="F11" s="98"/>
@@ -15570,7 +15525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="34"/>
       <c r="E12" s="14"/>
       <c r="F12" s="98"/>
@@ -15581,7 +15536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="34"/>
       <c r="E13" s="14"/>
       <c r="F13" s="98"/>
@@ -15592,7 +15547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="34"/>
       <c r="E14" s="14"/>
       <c r="F14" s="98"/>
@@ -15603,7 +15558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="34"/>
       <c r="E15" s="14"/>
       <c r="F15" s="98"/>
@@ -15614,7 +15569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="34"/>
       <c r="E16" s="14"/>
       <c r="F16" s="98"/>
@@ -15625,35 +15580,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E16" xr:uid="{083DF14A-00E2-452A-8599-A053B3BDEC80}">
@@ -15673,7 +15628,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M63"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15686,13 +15641,13 @@
     <col min="14" max="14" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
@@ -15705,12 +15660,12 @@
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
     </row>
-    <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="79" t="s">
         <v>221</v>
       </c>
@@ -15733,7 +15688,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="str">
         <f>"Liveweight sold"</f>
         <v>Liveweight sold</v>
@@ -15754,7 +15709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="str">
         <f>"Manure produced"</f>
         <v>Manure produced</v>
@@ -15775,7 +15730,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="str">
         <f>"Manure sold"</f>
         <v>Manure sold</v>
@@ -15796,7 +15751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="1" t="str">
         <f>"Percent income from liveweight sold"</f>
         <v>Percent income from liveweight sold</v>
@@ -15817,7 +15772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="1" t="str">
         <f>"Percent income from manure sold"</f>
         <v>Percent income from manure sold</v>
@@ -15838,18 +15793,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J14" s="84">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D15" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D17" s="79" t="s">
         <v>221</v>
       </c>
@@ -15872,7 +15827,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
@@ -15893,7 +15848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
@@ -15914,7 +15869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
@@ -15935,7 +15890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D21" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
@@ -15956,7 +15911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
@@ -15977,7 +15932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
@@ -15998,18 +15953,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J25" s="84">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D26" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="79" t="s">
         <v>221</v>
       </c>
@@ -16032,7 +15987,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="1" t="str">
         <f>"Head count"</f>
         <v>Head count</v>
@@ -16053,7 +16008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="str">
         <f>"Duration of stay"</f>
         <v>Duration of stay</v>
@@ -16068,7 +16023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="str">
         <f>"Diet - Feed intake"</f>
         <v>Diet - Feed intake</v>
@@ -16089,7 +16044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="str">
         <f>"Diet - Ether extract"</f>
         <v>Diet - Ether extract</v>
@@ -16110,7 +16065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="str">
         <f>"Diet - NDF"</f>
         <v>Diet - NDF</v>
@@ -16125,7 +16080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D34" s="1" t="str">
         <f>"Diet - Dry matter digestibility"</f>
         <v>Diet - Dry matter digestibility</v>
@@ -16140,7 +16095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="1" t="str">
         <f>"Diet - Crude protein"</f>
         <v>Diet - Crude protein</v>
@@ -16155,7 +16110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="1" t="str">
         <f>"Diet - Nitrogen retention"</f>
         <v>Diet - Nitrogen retention</v>
@@ -16170,7 +16125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="1" t="str">
         <f>"Production and manure management systems"</f>
         <v>Production and manure management systems</v>
@@ -16191,7 +16146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D38" s="1" t="str">
         <f>"Livestock sales"</f>
         <v>Livestock sales</v>
@@ -16206,7 +16161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D39" s="1" t="str">
         <f>"Livestock purchases"</f>
         <v>Livestock purchases</v>
@@ -16221,18 +16176,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J41" s="84">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D42" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="79" t="s">
         <v>221</v>
       </c>
@@ -16255,7 +16210,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
@@ -16276,7 +16231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
@@ -16297,7 +16252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
@@ -16318,7 +16273,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
@@ -16339,18 +16294,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J50" s="84">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D52" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="79" t="s">
         <v>221</v>
       </c>
@@ -16373,7 +16328,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
@@ -16394,7 +16349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
@@ -16415,7 +16370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
@@ -16436,7 +16391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="str">
         <f>"Use of contractors and service providers"</f>
         <v>Use of contractors and service providers</v>
@@ -16451,7 +16406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
@@ -16472,13 +16427,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J61" s="84">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D63" s="86" t="s">
         <v>228</v>
       </c>
@@ -16516,7 +16471,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="22" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="22" customWidth="1"/>
@@ -16549,10 +16504,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -16579,11 +16534,11 @@
       <c r="V3" s="24"/>
       <c r="W3" s="24"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="25"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -16591,7 +16546,7 @@
       </c>
       <c r="BM5" s="25"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81" t="s">
         <v>2</v>
       </c>
@@ -16605,7 +16560,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="82" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -16623,7 +16578,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -16641,7 +16596,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="20" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16656,7 +16611,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="20" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16671,7 +16626,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="20" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16687,7 +16642,7 @@
       </c>
       <c r="BM11" s="25"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="20" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16703,7 +16658,7 @@
       </c>
       <c r="BM12" s="25"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="20" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16718,7 +16673,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="20" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16733,129 +16688,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="20" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="20" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="20" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="20" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="20" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="20" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="20" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="20" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="20" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="20" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="20" t="s">
         <v>26</v>
@@ -16864,7 +16819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="20" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16875,7 +16830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="20" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16886,7 +16841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="20" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16897,7 +16852,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="20" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16908,7 +16863,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="20" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16919,7 +16874,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="20" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16930,7 +16885,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="20" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16941,24 +16896,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="20" t="s">
         <v>26</v>
@@ -16976,7 +16931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="20" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -16999,7 +16954,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="20" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17022,7 +16977,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="20" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17045,7 +17000,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="20" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17068,7 +17023,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="20" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17091,7 +17046,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="20" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17114,7 +17069,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="20" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17137,49 +17092,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="26" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="26" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="26" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="20" t="s">
         <v>32</v>
@@ -17188,7 +17143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="20" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17199,7 +17154,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="20" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17210,7 +17165,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="20" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17221,7 +17176,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="20" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17232,7 +17187,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="20" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17243,7 +17198,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="20" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17254,7 +17209,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="20" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17265,7 +17220,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="20" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17276,7 +17231,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="20" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17287,7 +17242,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="20" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17298,7 +17253,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="20" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17309,7 +17264,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="20" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17320,7 +17275,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="20" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17331,7 +17286,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="20" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17342,64 +17297,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="26" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="26" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="26" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="26" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="26" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="20" t="s">
         <v>32</v>
@@ -17451,7 +17406,7 @@
       </c>
       <c r="T89" s="20"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="20" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17519,7 +17474,7 @@
       </c>
       <c r="T90" s="20"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="20" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17587,7 +17542,7 @@
       </c>
       <c r="T91" s="20"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="20" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17655,7 +17610,7 @@
       </c>
       <c r="T92" s="20"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="20" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17723,7 +17678,7 @@
       </c>
       <c r="T93" s="20"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="20" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17791,7 +17746,7 @@
       </c>
       <c r="T94" s="20"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="20" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17859,7 +17814,7 @@
       </c>
       <c r="T95" s="20"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="20" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17927,7 +17882,7 @@
       </c>
       <c r="T96" s="20"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="20" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17995,66 +17950,66 @@
       </c>
       <c r="T97" s="20"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="26" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="20" t="s">
         <v>49</v>
@@ -18069,7 +18024,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="20" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18088,7 +18043,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="20" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18107,7 +18062,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="20" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18126,13 +18081,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18140,7 +18095,7 @@
       </c>
       <c r="BN115" s="22"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18148,7 +18103,7 @@
       </c>
       <c r="BN116" s="22"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="26" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18156,11 +18111,11 @@
       </c>
       <c r="BN117" s="22"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="22"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="20" t="s">
         <v>52</v>
@@ -18176,7 +18131,7 @@
       </c>
       <c r="BN119" s="22"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="20" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18196,7 +18151,7 @@
       </c>
       <c r="BN120" s="22"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="20" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18216,31 +18171,31 @@
       </c>
       <c r="BN121" s="22"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="22"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="20" t="s">
         <v>54</v>
@@ -18249,7 +18204,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="20" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18260,7 +18215,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="20" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18271,13 +18226,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18285,7 +18240,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18293,7 +18248,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>56</v>
@@ -18302,7 +18257,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18313,7 +18268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18324,10 +18279,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="22"/>
       <c r="BO138" s="22"/>
@@ -18342,7 +18297,7 @@
       <c r="BX138" s="22"/>
       <c r="BY138" s="22"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18361,7 +18316,7 @@
       <c r="BX139" s="22"/>
       <c r="BY139" s="22"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18380,7 +18335,7 @@
       <c r="BX140" s="22"/>
       <c r="BY140" s="22"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="26" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18388,7 +18343,7 @@
       </c>
       <c r="BN141" s="22"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="20" t="s">
         <v>58</v>
@@ -18398,7 +18353,7 @@
       </c>
       <c r="BN142" s="22"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="20" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18410,7 +18365,7 @@
       </c>
       <c r="BN143" s="22"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18422,7 +18377,7 @@
       </c>
       <c r="BN144" s="22"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18434,7 +18389,7 @@
       </c>
       <c r="BN145" s="22"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18446,7 +18401,7 @@
       </c>
       <c r="BN146" s="22"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18458,15 +18413,15 @@
       </c>
       <c r="BN147" s="22"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="22"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="22"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18474,7 +18429,7 @@
       </c>
       <c r="BN150" s="22"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18482,11 +18437,11 @@
       </c>
       <c r="BN151" s="22"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="22"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="20" t="s">
         <v>59</v>
@@ -18506,7 +18461,7 @@
       <c r="BL153" s="25"/>
       <c r="BM153" s="25"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="20" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18528,7 +18483,7 @@
       <c r="BL154" s="25"/>
       <c r="BM154" s="25"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="20" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18550,7 +18505,7 @@
       <c r="BL155" s="25"/>
       <c r="BM155" s="25"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="20" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18561,7 +18516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="20" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18572,7 +18527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="20" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18583,34 +18538,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -18619,17 +18574,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="22"/>
       <c r="BO165" s="22"/>
       <c r="BP165" s="22"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="22"/>
       <c r="BO166" s="22"/>
       <c r="BP166" s="22"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -18638,7 +18593,7 @@
       <c r="BO167" s="22"/>
       <c r="BP167" s="22"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -18647,7 +18602,7 @@
       <c r="BO168" s="22"/>
       <c r="BP168" s="22"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -18656,7 +18611,7 @@
       <c r="BO169" s="22"/>
       <c r="BP169" s="22"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -18668,17 +18623,17 @@
       <c r="BO170" s="22"/>
       <c r="BP170" s="22"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="22"/>
       <c r="BO171" s="22"/>
       <c r="BP171" s="22"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="22"/>
       <c r="BO172" s="22"/>
       <c r="BP172" s="22"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -18687,7 +18642,7 @@
       <c r="BO173" s="22"/>
       <c r="BP173" s="22"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -18696,7 +18651,7 @@
       <c r="BO174" s="22"/>
       <c r="BP174" s="22"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -18709,17 +18664,17 @@
       <c r="BO175" s="22"/>
       <c r="BP175" s="22"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="22"/>
       <c r="BO176" s="22"/>
       <c r="BP176" s="22"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="22"/>
       <c r="BO177" s="22"/>
       <c r="BP177" s="22"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -18728,7 +18683,7 @@
       <c r="BO178" s="22"/>
       <c r="BP178" s="22"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -18737,39 +18692,39 @@
       <c r="BO179" s="22"/>
       <c r="BP179" s="22"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="26" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="26" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="26" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="26" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="26" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="20" t="s">
         <v>61</v>
       </c>
@@ -18786,7 +18741,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="20" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -18808,7 +18763,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="20" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -18830,7 +18785,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="20" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18852,7 +18807,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="20" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18874,7 +18829,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="20" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -18896,7 +18851,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="20" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -18918,7 +18873,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="20" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -18940,7 +18895,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="20" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -18962,7 +18917,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="20" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -18984,7 +18939,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="20" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -19006,7 +18961,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="20" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19028,7 +18983,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="20" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19050,7 +19005,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="20" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19072,31 +19027,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="26" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="20" t="s">
         <v>32</v>
       </c>
@@ -19104,7 +19059,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="20" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19114,7 +19069,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19124,13 +19079,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="20" t="s">
         <v>67</v>
       </c>
@@ -19138,7 +19093,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="20" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19148,7 +19103,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19158,7 +19113,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19168,7 +19123,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19178,7 +19133,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19188,7 +19143,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19198,7 +19153,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19208,7 +19163,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19218,7 +19173,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19228,7 +19183,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19238,7 +19193,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19248,7 +19203,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19258,25 +19213,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="26" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="20" t="s">
         <v>69</v>
       </c>
@@ -19326,7 +19281,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="20" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19392,7 +19347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19458,7 +19413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19524,7 +19479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19590,7 +19545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19656,7 +19611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19722,7 +19677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19788,7 +19743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19854,7 +19809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19920,7 +19875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19986,7 +19941,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20052,7 +20007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20118,7 +20073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20184,7 +20139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20250,7 +20205,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20316,7 +20271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20382,7 +20337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20448,7 +20403,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20514,7 +20469,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20580,31 +20535,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="20" t="s">
         <v>85</v>
       </c>
@@ -20612,7 +20567,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="20" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -20622,7 +20577,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -20632,17 +20587,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="20" t="s">
         <v>199</v>
       </c>
@@ -20658,7 +20613,7 @@
       <c r="V265" s="1"/>
       <c r="BN265" s="22"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="20" t="s">
         <v>200</v>
       </c>
@@ -20674,7 +20629,7 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="22"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="20" t="s">
         <v>201</v>
       </c>
@@ -20690,7 +20645,7 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="22"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="20" t="s">
         <v>202</v>
       </c>
@@ -20706,7 +20661,7 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="22"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="20" t="s">
         <v>203</v>
       </c>
@@ -20722,7 +20677,7 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="22"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="20" t="s">
         <v>204</v>
       </c>
@@ -20738,12 +20693,12 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="22"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="20" t="s">
         <v>199</v>
       </c>
@@ -20759,7 +20714,7 @@
       <c r="V274" s="1"/>
       <c r="BN274" s="22"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="20" t="s">
         <v>205</v>
       </c>
@@ -20775,7 +20730,7 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="22"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="20" t="s">
         <v>206</v>
       </c>
@@ -20791,7 +20746,7 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="22"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="20" t="s">
         <v>207</v>
       </c>
@@ -20807,7 +20762,7 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="22"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="20" t="s">
         <v>208</v>
       </c>
@@ -20823,7 +20778,7 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="22"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="20" t="s">
         <v>209</v>
       </c>
@@ -20839,12 +20794,12 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="22"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="20" t="s">
         <v>199</v>
       </c>
@@ -20860,7 +20815,7 @@
       <c r="V283" s="1"/>
       <c r="BN283" s="22"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="20" t="s">
         <v>210</v>
       </c>
@@ -20876,7 +20831,7 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="22"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="20" t="s">
         <v>211</v>
       </c>
@@ -20892,7 +20847,7 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="22"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="20" t="s">
         <v>212</v>
       </c>
@@ -20908,7 +20863,7 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="22"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="20" t="s">
         <v>213</v>
       </c>
@@ -20924,7 +20879,7 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="22"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="20" t="s">
         <v>214</v>
       </c>
@@ -20940,12 +20895,12 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="22"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="20" t="s">
         <v>199</v>
       </c>
@@ -20961,7 +20916,7 @@
       <c r="V292" s="1"/>
       <c r="BN292" s="22"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="20" t="s">
         <v>215</v>
       </c>
@@ -20977,7 +20932,7 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="22"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="20" t="s">
         <v>216</v>
       </c>
@@ -20993,7 +20948,7 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="22"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="20" t="s">
         <v>217</v>
       </c>
@@ -21009,7 +20964,7 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="22"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="20" t="s">
         <v>218</v>
       </c>
@@ -21025,7 +20980,7 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="22"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="20" t="s">
         <v>219</v>
       </c>
